--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="current" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="current" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>412447.74</v>
+        <v>267605.81</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>93.02271253000001</v>
+        <v>86.81310058</v>
       </c>
       <c r="E2" t="n">
-        <v>383</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>28521.45</v>
+        <v>39275.92</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.43267592</v>
+        <v>12.74136908</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -526,17 +526,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2272.72</v>
+        <v>894.3099999999999</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.5125851300000001</v>
+        <v>0.2901201</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>142</v>
+        <v>479.06</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.03202642</v>
+        <v>0.15541024</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>443383.91</v>
+        <v>308255.1</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>457</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -637,17 +637,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2272.72</v>
+        <v>894.3099999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.5125851300000001</v>
+        <v>0.2901201</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>412447.74</v>
+        <v>267605.81</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>93.02271253000001</v>
+        <v>86.81310058</v>
       </c>
       <c r="E3" t="n">
-        <v>383</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>142</v>
+        <v>479.06</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.03202642</v>
+        <v>0.15541024</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>28521.45</v>
+        <v>39275.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.43267592</v>
+        <v>12.74136908</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>267605.81</v>
+        <v>461123.2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>86.81310058</v>
+        <v>92.95216732</v>
       </c>
       <c r="E2" t="n">
-        <v>340</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39275.92</v>
+        <v>33681.49</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.74136908</v>
+        <v>6.78943825</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -526,17 +526,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>894.3099999999999</v>
+        <v>948.86</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2901201</v>
+        <v>0.19126904</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>479.06</v>
+        <v>333</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.15541024</v>
+        <v>0.06712538</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>308255.1</v>
+        <v>496086.55</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>416</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -637,17 +637,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>894.3099999999999</v>
+        <v>948.86</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.2901201</v>
+        <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>267605.81</v>
+        <v>461123.2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>86.81310058</v>
+        <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
-        <v>340</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>479.06</v>
+        <v>333</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.15541024</v>
+        <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>39275.92</v>
+        <v>33681.49</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.74136908</v>
+        <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>461123.2</v>
+        <v>316928.34</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>92.95216732</v>
+        <v>76.20022474</v>
       </c>
       <c r="E2" t="n">
-        <v>377</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>33681.49</v>
+        <v>66159.13</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.78943825</v>
+        <v>15.90687843</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>948.86</v>
+        <v>28879.81</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.19126904</v>
+        <v>6.94367696</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>333</v>
+        <v>3947.95</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.06712538</v>
+        <v>0.94921987</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>496086.55</v>
+        <v>415915.23</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>444</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -713,6 +713,90 @@
         <v>62</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3947.95</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.94921987</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>316928.34</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>76.20022474</v>
+      </c>
+      <c r="E7" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>28879.81</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>6.94367696</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>66159.13</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>15.90687843</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>316928.34</v>
+        <v>506109.58</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.20022474</v>
+        <v>91.54108388</v>
       </c>
       <c r="E2" t="n">
-        <v>339</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>66159.13</v>
+        <v>32950.07</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15.90687843</v>
+        <v>5.95974714</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>28879.81</v>
+        <v>13144.61</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.94367696</v>
+        <v>2.37749273</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3947.95</v>
+        <v>672.72</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.94921987</v>
+        <v>0.12167625</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>415915.23</v>
+        <v>552876.98</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>399</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -797,6 +797,90 @@
         <v>45</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>672.72</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.12167625</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>506109.58</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>91.54108388</v>
+      </c>
+      <c r="E11" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>13144.61</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2.37749273</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>32950.07</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>5.95974714</v>
+      </c>
+      <c r="E13" t="n">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>506109.58</v>
+        <v>229609.87</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>91.54108388</v>
+        <v>86.83224112000001</v>
       </c>
       <c r="E2" t="n">
-        <v>302</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,76 +509,97 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32950.07</v>
+        <v>30122.92</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.95974714</v>
+        <v>11.39167342</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13144.61</v>
+        <v>3803.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.37749273</v>
+        <v>1.43836189</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>672.72</v>
+        <v>884.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.12167625</v>
+        <v>0.33432001</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.00340356</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>552876.98</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>264429.28</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>362</v>
+      <c r="E7" s="4" t="n">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -881,6 +902,111 @@
         <v>54</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.00340356</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3803.45</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1.43836189</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>229609.87</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>86.83224112000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>884.04</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.33432001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>30122.92</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>11.39167342</v>
+      </c>
+      <c r="E18" t="n">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>229609.87</v>
+        <v>451338.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>86.83224112000001</v>
+        <v>80.91052954</v>
       </c>
       <c r="E2" t="n">
-        <v>322</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,31 +509,31 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30122.92</v>
+        <v>62988</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>11.39167342</v>
+        <v>11.29173865</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3803.45</v>
+        <v>23268.18</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.43836189</v>
+        <v>4.17124226</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,55 +551,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>884.04</v>
+        <v>20229.42</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.33432001</v>
+        <v>3.62648955</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.00340356</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>264429.28</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>557823.75</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>398</v>
+      <c r="E6" s="4" t="n">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1007,6 +986,90 @@
         <v>71</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>23268.18</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.17124226</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>451338.15</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>80.91052954</v>
+      </c>
+      <c r="E20" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>20229.42</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.62648955</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>62988</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>11.29173865</v>
+      </c>
+      <c r="E22" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>451338.15</v>
+        <v>341584.75</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.91052954</v>
+        <v>96.16036696</v>
       </c>
       <c r="E2" t="n">
-        <v>274</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>62988</v>
+        <v>13253.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>11.29173865</v>
+        <v>3.7309073</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>23268.18</v>
+        <v>283.13</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.17124226</v>
+        <v>0.07970463</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20229.42</v>
+        <v>103.09</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.62648955</v>
+        <v>0.02902112</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>557823.75</v>
+        <v>355224.05</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>333</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,90 @@
         <v>45</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.02902112</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>283.13</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.07970463</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>341584.75</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>96.16036696</v>
+      </c>
+      <c r="E25" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>13253.08</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3.7309073</v>
+      </c>
+      <c r="E26" t="n">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>341584.75</v>
+        <v>366675.1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>96.16036696</v>
+        <v>88.88052623</v>
       </c>
       <c r="E2" t="n">
-        <v>324</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,76 +509,55 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13253.08</v>
+        <v>34905.37</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3.7309073</v>
+        <v>8.460917179999999</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>283.13</v>
+        <v>10967.83</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.07970463</v>
+        <v>2.65855659</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>103.09</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.02902112</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>355224.05</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>412548.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>382</v>
+      <c r="E5" s="4" t="n">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1154,6 +1133,69 @@
         <v>55</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>366675.1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>88.88052623</v>
+      </c>
+      <c r="E27" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>10967.83</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2.65855659</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>34905.37</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>8.460917179999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>366675.1</v>
+        <v>431085.81</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>88.88052623</v>
+        <v>81.83421629999999</v>
       </c>
       <c r="E2" t="n">
-        <v>283</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34905.37</v>
+        <v>94060.16</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.460917179999999</v>
+        <v>17.85570135</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10967.83</v>
+        <v>1633.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.65855659</v>
+        <v>0.31008235</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>412548.3</v>
+        <v>526779.42</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>344</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1196,6 +1196,69 @@
         <v>58</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>431085.81</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>81.83421629999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1633.45</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.31008235</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>94060.16</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>17.85570135</v>
+      </c>
+      <c r="E32" t="n">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>431085.81</v>
+        <v>321805.16</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>81.83421629999999</v>
+        <v>78.53984421</v>
       </c>
       <c r="E2" t="n">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>94060.16</v>
+        <v>81063.48</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.85570135</v>
+        <v>19.78437229</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1633.45</v>
+        <v>6866.27</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.31008235</v>
+        <v>1.6757835</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>526779.42</v>
+        <v>409734.91</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>447</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1259,6 +1259,69 @@
         <v>73</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>321805.16</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>78.53984421</v>
+      </c>
+      <c r="E33" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>81063.48</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>19.78437229</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>6866.27</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1.6757835</v>
+      </c>
+      <c r="E35" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>321805.16</v>
+        <v>352851.14</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.53984421</v>
+        <v>94.15474251000001</v>
       </c>
       <c r="E2" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>81063.48</v>
+        <v>21329</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.78437229</v>
+        <v>5.69142699</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6866.27</v>
+        <v>576.49</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.6757835</v>
+        <v>0.1538305</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>409734.91</v>
+        <v>374756.63</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>378</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1322,6 +1322,69 @@
         <v>41</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>352851.14</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>94.15474251000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>576.49</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.1538305</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>21329</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.69142699</v>
+      </c>
+      <c r="E38" t="n">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>352851.14</v>
+        <v>509873.13</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>94.15474251000001</v>
+        <v>89.54027855</v>
       </c>
       <c r="E2" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>21329</v>
+        <v>50957.5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.69142699</v>
+        <v>8.94879231</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,34 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>576.49</v>
+        <v>8520.23</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1538305</v>
+        <v>1.49626196</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.01466719</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>374756.63</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>569434.38</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>401</v>
+      <c r="E6" s="4" t="n">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1385,6 +1406,90 @@
         <v>56</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.01466719</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>509873.13</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>89.54027855</v>
+      </c>
+      <c r="E40" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>8520.23</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1.49626196</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>50957.5</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>8.94879231</v>
+      </c>
+      <c r="E42" t="n">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>509873.13</v>
+        <v>510341.61</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>89.54027855</v>
+        <v>89.00516713</v>
       </c>
       <c r="E2" t="n">
-        <v>341</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>50957.5</v>
+        <v>51199.45</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.94879231</v>
+        <v>8.92934363</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8520.23</v>
+        <v>9326.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.49626196</v>
+        <v>1.62650962</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>83.52</v>
+        <v>2517.04</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.01466719</v>
+        <v>0.43897962</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>569434.38</v>
+        <v>573384.25</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>409</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1490,6 +1490,90 @@
         <v>62</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>9326.15</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1.62650962</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>510341.61</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>89.00516713</v>
+      </c>
+      <c r="E44" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2517.04</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.43897962</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>51199.45</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>8.92934363</v>
+      </c>
+      <c r="E46" t="n">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>510341.61</v>
+        <v>270843.56</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>89.00516713</v>
+        <v>80.62440645</v>
       </c>
       <c r="E2" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,31 +509,31 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>51199.45</v>
+        <v>62402.91</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.92934363</v>
+        <v>18.57602809</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9326.15</v>
+        <v>1223.36</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.62650962</v>
+        <v>0.36416843</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -542,43 +542,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.25302704</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>2517.04</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.43897962</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>612.64</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.18236999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>573384.25</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>335932.47</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>345</v>
+      <c r="E7" s="4" t="n">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1574,6 +1595,111 @@
         <v>53</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.25302704</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1223.36</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.36416843</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>270843.56</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>80.62440645</v>
+      </c>
+      <c r="E49" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>612.64</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.18236999</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>62402.91</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>18.57602809</v>
+      </c>
+      <c r="E51" t="n">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>270843.56</v>
+        <v>555930.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.62440645</v>
+        <v>91.1452503</v>
       </c>
       <c r="E2" t="n">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,55 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>62402.91</v>
+        <v>52417.67</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.57602809</v>
+        <v>8.59392033</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1223.36</v>
+        <v>1590.9</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.36416843</v>
+        <v>0.26082937</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.25302704</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>612.64</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.18236999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>335932.47</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>609938.98</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>346</v>
+      <c r="E5" s="4" t="n">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1658,69 @@
         <v>44</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>555930.41</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>91.1452503</v>
+      </c>
+      <c r="E52" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1590.9</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.26082937</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>52417.67</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>8.59392033</v>
+      </c>
+      <c r="E54" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>555930.41</v>
+        <v>319888.32</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>91.1452503</v>
+        <v>87.05305848</v>
       </c>
       <c r="E2" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>52417.67</v>
+        <v>46286.58</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.59392033</v>
+        <v>12.5962347</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,34 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1590.9</v>
+        <v>1278.17</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.26082937</v>
+        <v>0.34783579</v>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.00287103</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>609938.98</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>367463.62</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>353</v>
+      <c r="E6" s="4" t="n">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1721,6 +1742,90 @@
         <v>50</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.00287103</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>319888.32</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>87.05305848</v>
+      </c>
+      <c r="E56" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1278.17</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.34783579</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46286.58</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>12.5962347</v>
+      </c>
+      <c r="E58" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>319888.32</v>
+        <v>264522.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>87.05305848</v>
+        <v>87.4504938</v>
       </c>
       <c r="E2" t="n">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46286.58</v>
+        <v>36334.49</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.5962347</v>
+        <v>12.01210292</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1278.17</v>
+        <v>1149.77</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.34783579</v>
+        <v>0.38011145</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -542,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,34 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10.55</v>
+        <v>354.29</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.00287103</v>
+        <v>0.1171275</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>121.49</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.04016433</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>367463.62</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>302482.34</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>475</v>
+      <c r="E7" s="4" t="n">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1826,6 +1847,111 @@
         <v>95</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>354.29</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.1171275</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>121.49</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.04016433</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>264522.3</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>87.4504938</v>
+      </c>
+      <c r="E61" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1149.77</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.38011145</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>36334.49</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>12.01210292</v>
+      </c>
+      <c r="E63" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>264522.3</v>
+        <v>284866.12</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>87.4504938</v>
+        <v>77.73852608</v>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,73 +509,73 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36334.49</v>
+        <v>74564.85000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.01210292</v>
+        <v>20.34837115</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1149.77</v>
+        <v>4545.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.38011145</v>
+        <v>1.24043036</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>354.29</v>
+        <v>1590.95</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.1171275</v>
+        <v>0.43416222</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>121.49</v>
+        <v>874</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.04016433</v>
+        <v>0.23851019</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>302482.34</v>
+        <v>366441.37</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>449</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1952,6 +1952,111 @@
         <v>76</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>4545.45</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1.24043036</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.23851019</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>284866.12</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>77.73852608</v>
+      </c>
+      <c r="E66" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1590.95</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.43416222</v>
+      </c>
+      <c r="E67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>74564.85000000001</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>20.34837115</v>
+      </c>
+      <c r="E68" t="n">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>284866.12</v>
+        <v>442814.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>77.73852608</v>
+        <v>80.48822254</v>
       </c>
       <c r="E2" t="n">
-        <v>319</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,55 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>74564.85000000001</v>
+        <v>106431.64</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.34837115</v>
+        <v>19.34557314</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4545.45</v>
+        <v>914.39</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.24043036</v>
+        <v>0.16620432</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1590.95</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.43416222</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>874</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.23851019</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>366441.37</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>550160.1800000001</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>387</v>
+      <c r="E5" s="4" t="n">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2015,69 @@
         <v>57</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>442814.15</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>80.48822254</v>
+      </c>
+      <c r="E69" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>914.39</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.16620432</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>106431.64</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>19.34557314</v>
+      </c>
+      <c r="E71" t="n">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>442814.15</v>
+        <v>528120.33</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.48822254</v>
+        <v>91.56712743999999</v>
       </c>
       <c r="E2" t="n">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>106431.64</v>
+        <v>47822.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.34557314</v>
+        <v>8.29153934</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,34 +530,76 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>914.39</v>
+        <v>567.3200000000001</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.16620432</v>
+        <v>0.09836369</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.02878159</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01418794</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>550160.1800000001</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>576757.5600000001</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>405</v>
+      <c r="E7" s="4" t="n">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2120,111 @@
         <v>58</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.02878159</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.01418794</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>528120.33</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>91.56712743999999</v>
+      </c>
+      <c r="E74" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>567.3200000000001</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.09836369</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>47822.08</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>8.29153934</v>
+      </c>
+      <c r="E76" t="n">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>528120.33</v>
+        <v>177127.26</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>91.56712743999999</v>
+        <v>82.68807579999999</v>
       </c>
       <c r="E2" t="n">
-        <v>331</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,76 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>47822.08</v>
+        <v>34100.64</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.29153934</v>
+        <v>15.91915499</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>567.3200000000001</v>
+        <v>2157.29</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.09836369</v>
+        <v>1.00708473</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>166</v>
+        <v>826.1799999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.02878159</v>
+        <v>0.38568448</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>81.83</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.01418794</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>576757.5600000001</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>214211.37</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>420</v>
+      <c r="E6" s="4" t="n">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2204,90 @@
         <v>82</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>2157.29</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1.00708473</v>
+      </c>
+      <c r="E77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>177127.26</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>82.68807579999999</v>
+      </c>
+      <c r="E78" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>826.1799999999999</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.38568448</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>34100.64</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>15.91915499</v>
+      </c>
+      <c r="E80" t="n">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>177127.26</v>
+        <v>214416.2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.68807579999999</v>
+        <v>69.21875842999999</v>
       </c>
       <c r="E2" t="n">
-        <v>312</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34100.64</v>
+        <v>64397.95</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15.91915499</v>
+        <v>20.78922276</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2157.29</v>
+        <v>21771.31</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.00708473</v>
+        <v>7.02830778</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,34 +551,76 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>826.1799999999999</v>
+        <v>9060.450000000001</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.38568448</v>
+        <v>2.92493338</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.0213064</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.01747125</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>214211.37</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>309766.03</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>415</v>
+      <c r="E8" s="4" t="n">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2330,132 @@
         <v>89</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0.01747125</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0.0213064</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>21771.31</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>7.02830778</v>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>214416.2</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>69.21875842999999</v>
+      </c>
+      <c r="E84" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>9060.450000000001</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>2.92493338</v>
+      </c>
+      <c r="E85" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>64397.95</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>20.78922276</v>
+      </c>
+      <c r="E86" t="n">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>214416.2</v>
+        <v>260988.37</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>69.21875842999999</v>
+        <v>72.53941456</v>
       </c>
       <c r="E2" t="n">
-        <v>259</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,118 +509,76 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>64397.95</v>
+        <v>90209.81</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.78922276</v>
+        <v>25.07302071</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>21771.31</v>
+        <v>7522.28</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.02830778</v>
+        <v>2.09075135</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9060.450000000001</v>
+        <v>1067.9</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.92493338</v>
+        <v>0.29681338</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.0213064</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>54.12</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.01747125</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>309766.03</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>359788.36</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>367</v>
+      <c r="E6" s="4" t="n">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2456,6 +2414,90 @@
         <v>85</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1067.9</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.29681338</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>260988.37</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>72.53941456</v>
+      </c>
+      <c r="E88" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>7522.28</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>2.09075135</v>
+      </c>
+      <c r="E89" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>90209.81</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>25.07302071</v>
+      </c>
+      <c r="E90" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>260988.37</v>
+        <v>201888.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>72.53941456</v>
+        <v>60.81398972</v>
       </c>
       <c r="E2" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>90209.81</v>
+        <v>103460.15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>25.07302071</v>
+        <v>31.1648623</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7522.28</v>
+        <v>15503.87</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.09075135</v>
+        <v>4.67016502</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1067.9</v>
+        <v>11124.49</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.29681338</v>
+        <v>3.35098295</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>359788.36</v>
+        <v>331976.92</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>337</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2498,6 +2498,90 @@
         <v>110</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>11124.49</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>3.35098295</v>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>201888.41</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>60.81398972</v>
+      </c>
+      <c r="E92" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>15503.87</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>4.67016502</v>
+      </c>
+      <c r="E93" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>103460.15</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>31.1648623</v>
+      </c>
+      <c r="E94" t="n">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>201888.41</v>
+        <v>173800.98</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>60.81398972</v>
+        <v>53.20604405</v>
       </c>
       <c r="E2" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>103460.15</v>
+        <v>126297.98</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>31.1648623</v>
+        <v>38.66385499</v>
       </c>
       <c r="E3" t="n">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15503.87</v>
+        <v>23680.09</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.67016502</v>
+        <v>7.24923364</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,34 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11124.49</v>
+        <v>1848</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.35098295</v>
+        <v>0.56573196</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1029.41</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.31513536</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>331976.92</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>326656.46</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>396</v>
+      <c r="E7" s="4" t="n">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2582,6 +2603,111 @@
         <v>163</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1029.41</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.31513536</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.56573196</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>126297.98</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>38.66385499</v>
+      </c>
+      <c r="E97" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>23680.09</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>7.24923364</v>
+      </c>
+      <c r="E98" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>173800.98</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>53.20604405</v>
+      </c>
+      <c r="E99" t="n">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>173800.98</v>
+        <v>296012.79</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>53.20604405</v>
+        <v>78.65181887</v>
       </c>
       <c r="E2" t="n">
-        <v>196</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>126297.98</v>
+        <v>75770.75</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38.66385499</v>
+        <v>20.13260071</v>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,52 +530,52 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>23680.09</v>
+        <v>3709.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.24923364</v>
+        <v>0.98553645</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1848</v>
+        <v>856.11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.56573196</v>
+        <v>0.22747196</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1029.41</v>
+        <v>9.68</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.31513536</v>
+        <v>0.00257202</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>326656.46</v>
+        <v>376358.48</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>402</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2708,6 +2708,111 @@
         <v>196</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>856.11</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0.22747196</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.00257202</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>296012.79</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>78.65181887</v>
+      </c>
+      <c r="E102" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>3709.15</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.98553645</v>
+      </c>
+      <c r="E103" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>75770.75</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>20.13260071</v>
+      </c>
+      <c r="E104" t="n">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>296012.79</v>
+        <v>303265.05</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.65181887</v>
+        <v>81.67502655</v>
       </c>
       <c r="E2" t="n">
-        <v>428</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>75770.75</v>
+        <v>66848.86</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.13260071</v>
+        <v>18.00366516</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3709.15</v>
+        <v>829.42</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.98553645</v>
+        <v>0.22337853</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>856.11</v>
+        <v>363.62</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.22747196</v>
+        <v>0.09792976</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.00257202</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>376358.48</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>371306.95</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>534</v>
+      <c r="E6" s="4" t="n">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2813,6 +2792,90 @@
         <v>94</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0.09792976</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>303265.05</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>81.67502655</v>
+      </c>
+      <c r="E106" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>829.42</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.22337853</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>66848.86</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>18.00366516</v>
+      </c>
+      <c r="E108" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>303265.05</v>
+        <v>174192.16</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>81.67502655</v>
+        <v>66.86566559000001</v>
       </c>
       <c r="E2" t="n">
-        <v>372</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>66848.86</v>
+        <v>66880.21000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.00366516</v>
+        <v>25.67273841</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,55 +530,34 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>829.42</v>
+        <v>19438.25</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.22337853</v>
+        <v>7.461596</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>363.62</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.09792976</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>371306.95</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>260510.62</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>484</v>
+      <c r="E5" s="4" t="n">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2876,6 +2855,69 @@
         <v>107</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>174192.16</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>66.86566559000001</v>
+      </c>
+      <c r="E109" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>19438.25</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>7.461596</v>
+      </c>
+      <c r="E110" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>66880.21000000001</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>25.67273841</v>
+      </c>
+      <c r="E111" t="n">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>174192.16</v>
+        <v>202289.9</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.86566559000001</v>
+        <v>54.78137012</v>
       </c>
       <c r="E2" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>66880.21000000001</v>
+        <v>131943.66</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>25.67273841</v>
+        <v>35.73116836</v>
       </c>
       <c r="E3" t="n">
-        <v>122</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,34 +530,97 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19438.25</v>
+        <v>30328.46</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.461596</v>
+        <v>8.213136649999999</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2177.75</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.58974832</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1885.29</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.5105483200000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>642.63</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.17402822</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>260510.62</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>369267.69</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>384</v>
+      <c r="E8" s="4" t="n">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2918,6 +2981,132 @@
         <v>122</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>1885.29</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0.5105483200000001</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>642.63</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0.17402822</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>2177.75</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0.58974832</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>202289.9</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>54.78137012</v>
+      </c>
+      <c r="E115" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>30328.46</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>8.213136649999999</v>
+      </c>
+      <c r="E116" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>131943.66</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>35.73116836</v>
+      </c>
+      <c r="E117" t="n">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>202289.9</v>
+        <v>167439.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.78137012</v>
+        <v>62.62863161</v>
       </c>
       <c r="E2" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>131943.66</v>
+        <v>92453.32000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>35.73116836</v>
+        <v>34.58103874</v>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,97 +530,76 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>30328.46</v>
+        <v>7300.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.213136649999999</v>
+        <v>2.73058833</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2177.75</v>
+        <v>101.72</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.58974832</v>
+        <v>0.03804713</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1885.29</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.5105483200000001</v>
+        <v>0.02169419</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>642.63</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.17402822</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>369267.69</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>267352.64</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>446</v>
+      <c r="E7" s="4" t="n">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3107,6 +3086,111 @@
         <v>174</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>101.72</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0.03804713</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0.02169419</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>167439.3</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>62.62863161</v>
+      </c>
+      <c r="E120" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>7300.3</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>2.73058833</v>
+      </c>
+      <c r="E121" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>92453.32000000001</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>34.58103874</v>
+      </c>
+      <c r="E122" t="n">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>167439.3</v>
+        <v>232354.93</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.62863161</v>
+        <v>52.61642084</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>92453.32000000001</v>
+        <v>194477.52</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>34.58103874</v>
+        <v>44.0391389</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7300.3</v>
+        <v>11084.31</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.73058833</v>
+        <v>2.51002516</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
@@ -542,49 +542,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>101.72</v>
+        <v>2209.05</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.03804713</v>
+        <v>0.50023602</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>58</v>
+        <v>1475.74</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.02169419</v>
+        <v>0.33417908</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>267352.64</v>
+        <v>441601.55</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>429</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3191,6 +3191,111 @@
         <v>165</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>1475.74</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0.33417908</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>2209.05</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0.50023602</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>232354.93</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>52.61642084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>11084.31</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>2.51002516</v>
+      </c>
+      <c r="E126" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>194477.52</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>44.0391389</v>
+      </c>
+      <c r="E127" t="n">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>232354.93</v>
+        <v>233512.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>52.61642084</v>
+        <v>49.58956523</v>
       </c>
       <c r="E2" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>194477.52</v>
+        <v>222684.94</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.0391389</v>
+        <v>47.29025603</v>
       </c>
       <c r="E3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,97 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11084.31</v>
+        <v>10642.51</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.51002516</v>
+        <v>2.26008558</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2209.05</v>
+        <v>2990.78</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.50023602</v>
+        <v>0.63513389</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1475.74</v>
+        <v>847.45</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.33417908</v>
+        <v>0.17996784</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>211.86</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.04499143</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>441601.55</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>470889.69</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>465</v>
+      <c r="E8" s="4" t="n">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3296,6 +3317,132 @@
         <v>212</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>2990.78</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.63513389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>847.45</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.17996784</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>211.86</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.04499143</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>222684.94</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>47.29025603</v>
+      </c>
+      <c r="E131" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>10642.51</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>2.26008558</v>
+      </c>
+      <c r="E132" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>233512.15</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>49.58956523</v>
+      </c>
+      <c r="E133" t="n">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>233512.15</v>
+        <v>193052.4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>49.58956523</v>
+        <v>56.60080297</v>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>222684.94</v>
+        <v>133738.48</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>47.29025603</v>
+        <v>39.21062549</v>
       </c>
       <c r="E3" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10642.51</v>
+        <v>9278.84</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.26008558</v>
+        <v>2.72045204</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2990.78</v>
+        <v>2894.67</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.63513389</v>
+        <v>0.84868485</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,55 +572,34 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>847.45</v>
+        <v>2112.75</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.17996784</v>
+        <v>0.61943465</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>211.86</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.04499143</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>470889.69</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>341077.14</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>473</v>
+      <c r="E7" s="4" t="n">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3422,111 @@
         <v>245</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>2894.67</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0.84868485</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>2112.75</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0.61943465</v>
+      </c>
+      <c r="E135" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>133738.48</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>39.21062549</v>
+      </c>
+      <c r="E136" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>9278.84</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>2.72045204</v>
+      </c>
+      <c r="E137" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>193052.4</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>56.60080297</v>
+      </c>
+      <c r="E138" t="n">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>193052.4</v>
+        <v>165616.96</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>56.60080297</v>
+        <v>48.39329811</v>
       </c>
       <c r="E2" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>133738.48</v>
+        <v>161886.22</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>39.21062549</v>
+        <v>47.30317538</v>
       </c>
       <c r="E3" t="n">
-        <v>212</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9278.84</v>
+        <v>14589.85</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.72045204</v>
+        <v>4.26315614</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2894.67</v>
+        <v>138.16</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.84868485</v>
+        <v>0.04037037</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2112.75</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.61943465</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>341077.14</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>342231.19</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>462</v>
+      <c r="E6" s="4" t="n">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3527,6 +3506,90 @@
         <v>231</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>138.16</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0.04037037</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>165616.96</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>48.39329811</v>
+      </c>
+      <c r="E140" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>14589.85</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>4.26315614</v>
+      </c>
+      <c r="E141" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>161886.22</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>47.30317538</v>
+      </c>
+      <c r="E142" t="n">
+        <v>274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,91 +479,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>165616.96</v>
+        <v>397745.9</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>48.39329811</v>
+        <v>66.75017447</v>
       </c>
       <c r="E2" t="n">
-        <v>194</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>161886.22</v>
+        <v>142325.87</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>47.30317538</v>
+        <v>23.88529122</v>
       </c>
       <c r="E3" t="n">
-        <v>274</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14589.85</v>
+        <v>39179.97</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.26315614</v>
+        <v>6.57522763</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>138.16</v>
+        <v>16620.71</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.04037037</v>
+        <v>2.78930667</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>342231.19</v>
+        <v>595872.45</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>491</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3590,6 +3590,90 @@
         <v>274</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>39179.97</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>6.57522763</v>
+      </c>
+      <c r="E143" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>142325.87</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>23.88529122</v>
+      </c>
+      <c r="E144" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>16620.71</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>2.78930667</v>
+      </c>
+      <c r="E145" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>397745.9</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>66.75017447</v>
+      </c>
+      <c r="E146" t="n">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,82 +488,82 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>397745.9</v>
+        <v>231749.58</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.75017447</v>
+        <v>79.37696964</v>
       </c>
       <c r="E2" t="n">
-        <v>249</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>142325.87</v>
+        <v>54421.47</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.88529122</v>
+        <v>18.63999655</v>
       </c>
       <c r="E3" t="n">
-        <v>161</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>39179.97</v>
+        <v>4545.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.57522763</v>
+        <v>1.55687034</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16620.71</v>
+        <v>1244.23</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.78930667</v>
+        <v>0.42616348</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>595872.45</v>
+        <v>291960.73</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>445</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3674,6 +3674,90 @@
         <v>249</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>1244.23</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0.42616348</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>4545.45</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>1.55687034</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>54421.47</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>18.63999655</v>
+      </c>
+      <c r="E149" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>231749.58</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>79.37696964</v>
+      </c>
+      <c r="E150" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>231749.58</v>
+        <v>261951.9</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>79.37696964</v>
+        <v>61.03824</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,76 +509,118 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>54421.47</v>
+        <v>163136.27</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.63999655</v>
+        <v>38.01289779</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4545.45</v>
+        <v>3725.16</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.55687034</v>
+        <v>0.8680113</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>309.27</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.07206398</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1244.23</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.42616348</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.00689719</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.00188974</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>291960.73</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>429160.31</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>469</v>
+      <c r="E8" s="4" t="n">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3758,6 +3800,132 @@
         <v>400</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>0.00689719</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>309.27</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0.07206398</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>3725.16</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0.8680113</v>
+      </c>
+      <c r="E153" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0.00188974</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>163136.27</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>38.01289779</v>
+      </c>
+      <c r="E155" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>261951.9</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>61.03824</v>
+      </c>
+      <c r="E156" t="n">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>261951.9</v>
+        <v>298725.7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>61.03824</v>
+        <v>88.42379861000001</v>
       </c>
       <c r="E2" t="n">
-        <v>333</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>163136.27</v>
+        <v>32670.17</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38.01289779</v>
+        <v>9.670478749999999</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,31 +530,31 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3725.16</v>
+        <v>5382.13</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.8680113</v>
+        <v>1.59312834</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>309.27</v>
+        <v>909.09</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.07206398</v>
+        <v>0.26909366</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -563,19 +563,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>29.6</v>
+        <v>91.41</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.00689719</v>
+        <v>0.02705766</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,19 +584,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>55.55</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.00188974</v>
+        <v>0.01644298</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>429160.31</v>
+        <v>337834.05</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>410</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3926,6 +3926,132 @@
         <v>333</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0.01644298</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0.02705766</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>5382.13</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1.59312834</v>
+      </c>
+      <c r="E159" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>909.09</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0.26909366</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>32670.17</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>9.670478749999999</v>
+      </c>
+      <c r="E161" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>298725.7</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>88.42379861000001</v>
+      </c>
+      <c r="E162" t="n">
+        <v>418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>298725.7</v>
+        <v>269065.18</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>88.42379861000001</v>
+        <v>76.74470549</v>
       </c>
       <c r="E2" t="n">
-        <v>418</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32670.17</v>
+        <v>69940.2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.670478749999999</v>
+        <v>19.94884679</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5382.13</v>
+        <v>9919.66</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.59312834</v>
+        <v>2.82935676</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,76 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>909.09</v>
+        <v>1385.01</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.26909366</v>
+        <v>0.39504251</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>91.41</v>
+        <v>287.66</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.02705766</v>
+        <v>0.08204844999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.01644298</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>337834.05</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>350597.71</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>453</v>
+      <c r="E7" s="4" t="n">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4052,6 +4031,111 @@
         <v>418</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>287.66</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0.08204844999999999</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>9919.66</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>2.82935676</v>
+      </c>
+      <c r="E164" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>1385.01</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0.39504251</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>69940.2</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>19.94884679</v>
+      </c>
+      <c r="E166" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>269065.18</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>76.74470549</v>
+      </c>
+      <c r="E167" t="n">
+        <v>387</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>269065.18</v>
+        <v>359752.57</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.74470549</v>
+        <v>96.81870670000001</v>
       </c>
       <c r="E2" t="n">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,118 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69940.2</v>
+        <v>7627.33</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.94884679</v>
+        <v>2.05271147</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9919.66</v>
+        <v>3342.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.82935676</v>
+        <v>0.89945887</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1385.01</v>
+        <v>580.2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.39504251</v>
+        <v>0.1561468</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>287.66</v>
+        <v>172.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.08204844999999999</v>
+        <v>0.04648341</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.02649275</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>350597.71</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>371573.41</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>489</v>
+      <c r="E8" s="4" t="n">
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4136,6 +4157,132 @@
         <v>387</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>580.2</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0.1561468</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0.02649275</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>172.72</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0.04648341</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>3342.15</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0.89945887</v>
+      </c>
+      <c r="E171" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>7627.33</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>2.05271147</v>
+      </c>
+      <c r="E172" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>359752.57</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>96.81870670000001</v>
+      </c>
+      <c r="E173" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>359752.57</v>
+        <v>239054.29</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>96.81870670000001</v>
+        <v>83.63924057</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7627.33</v>
+        <v>36051.27</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.05271147</v>
+        <v>12.61345632</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,97 +530,76 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3342.15</v>
+        <v>10426.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.89945887</v>
+        <v>3.64795946</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>580.2</v>
+        <v>222</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.1561468</v>
+        <v>0.07767236</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>172.72</v>
+        <v>61.94</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.04648341</v>
+        <v>0.02167129</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>98.44</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.02649275</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>371573.41</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>285815.95</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>418</v>
+      <c r="E7" s="4" t="n">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4283,6 +4262,111 @@
         <v>400</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0.02167129</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>0.07767236</v>
+      </c>
+      <c r="E175" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>10426.45</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>3.64795946</v>
+      </c>
+      <c r="E176" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>36051.27</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>12.61345632</v>
+      </c>
+      <c r="E177" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>239054.29</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>83.63924057</v>
+      </c>
+      <c r="E178" t="n">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>239054.29</v>
+        <v>482598.55</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>83.63924057</v>
+        <v>72.28429297</v>
       </c>
       <c r="E2" t="n">
-        <v>305</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36051.27</v>
+        <v>158698.51</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.61345632</v>
+        <v>23.77008715</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,52 +530,52 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10426.45</v>
+        <v>23400.38</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.64795946</v>
+        <v>3.50494199</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>222</v>
+        <v>1971.96</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.07767236</v>
+        <v>0.29536296</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>61.94</v>
+        <v>970.1799999999999</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.02167129</v>
+        <v>0.14531493</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>285815.95</v>
+        <v>667639.58</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>379</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4367,6 +4367,111 @@
         <v>305</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>1971.96</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0.29536296</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>970.1799999999999</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0.14531493</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>23400.38</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>3.50494199</v>
+      </c>
+      <c r="E181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>158698.51</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>23.77008715</v>
+      </c>
+      <c r="E182" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>482598.55</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>72.28429297</v>
+      </c>
+      <c r="E183" t="n">
+        <v>337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>482598.55</v>
+        <v>412540.12</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>72.28429297</v>
+        <v>89.4695669</v>
       </c>
       <c r="E2" t="n">
-        <v>337</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,40 +509,40 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>158698.51</v>
+        <v>43002.78</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.77008715</v>
+        <v>9.326220449999999</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>23400.38</v>
+        <v>5203.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.50494199</v>
+        <v>1.12843225</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,55 +551,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1971.96</v>
+        <v>349.42</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.29536296</v>
+        <v>0.0757804</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>970.1799999999999</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.14531493</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>667639.58</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>461095.47</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>403</v>
+      <c r="E6" s="4" t="n">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4472,6 +4451,90 @@
         <v>337</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0.0757804</v>
+      </c>
+      <c r="E184" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>5203.15</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>1.12843225</v>
+      </c>
+      <c r="E185" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>43002.78</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>9.326220449999999</v>
+      </c>
+      <c r="E186" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>412540.12</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>89.4695669</v>
+      </c>
+      <c r="E187" t="n">
+        <v>420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>412540.12</v>
+        <v>328906.14</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>89.4695669</v>
+        <v>91.34164317</v>
       </c>
       <c r="E2" t="n">
-        <v>420</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>43002.78</v>
+        <v>29461.66</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.326220449999999</v>
+        <v>8.18189784</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5203.15</v>
+        <v>1231.47</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.12843225</v>
+        <v>0.34199572</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>349.42</v>
+        <v>484.18</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0757804</v>
+        <v>0.13446328</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>461095.47</v>
+        <v>360083.45</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>452</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4535,6 +4535,90 @@
         <v>420</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>1231.47</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0.34199572</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>484.18</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>0.13446328</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>29461.66</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>8.18189784</v>
+      </c>
+      <c r="E190" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>328906.14</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>91.34164317</v>
+      </c>
+      <c r="E191" t="n">
+        <v>384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>328906.14</v>
+        <v>441742.62</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>91.34164317</v>
+        <v>88.80732037999999</v>
       </c>
       <c r="E2" t="n">
-        <v>384</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>29461.66</v>
+        <v>42522.52</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.18189784</v>
+        <v>8.548668129999999</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1231.47</v>
+        <v>13128.29</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.34199572</v>
+        <v>2.63929312</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>484.18</v>
+        <v>23.47</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.13446328</v>
+        <v>0.00471838</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>360083.45</v>
+        <v>497416.9</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>408</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4619,6 +4619,90 @@
         <v>384</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>0.00471838</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>13128.29</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>2.63929312</v>
+      </c>
+      <c r="E193" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>42522.52</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>8.548668129999999</v>
+      </c>
+      <c r="E194" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>441742.62</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>88.80732037999999</v>
+      </c>
+      <c r="E195" t="n">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>441742.62</v>
+        <v>423550.36</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>88.80732037999999</v>
+        <v>82.40753461</v>
       </c>
       <c r="E2" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,40 +509,40 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>42522.52</v>
+        <v>45623.94</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.548668129999999</v>
+        <v>8.876763589999999</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13128.29</v>
+        <v>29796.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.63929312</v>
+        <v>5.79727904</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,34 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>23.47</v>
+        <v>14510.35</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.00471838</v>
+        <v>2.82318771</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>489.48</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.09523505</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>497416.9</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>513970.43</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>339</v>
+      <c r="E7" s="4" t="n">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4703,6 +4724,111 @@
         <v>299</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>14510.35</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>2.82318771</v>
+      </c>
+      <c r="E196" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>29796.3</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>5.79727904</v>
+      </c>
+      <c r="E197" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>489.48</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0.09523505</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>45623.94</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>8.876763589999999</v>
+      </c>
+      <c r="E199" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>423550.36</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>82.40753461</v>
+      </c>
+      <c r="E200" t="n">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>423550.36</v>
+        <v>403160.13</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.40753461</v>
+        <v>79.97561018</v>
       </c>
       <c r="E2" t="n">
-        <v>303</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45623.94</v>
+        <v>71555.96000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.876763589999999</v>
+        <v>14.19468627</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,61 +530,61 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>29796.3</v>
+        <v>19389.84</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.79727904</v>
+        <v>3.84639792</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14510.35</v>
+        <v>7103.09</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.82318771</v>
+        <v>1.40905292</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>489.48</v>
+        <v>2894.83</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.09523505</v>
+        <v>0.57425271</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>513970.43</v>
+        <v>504103.85</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>371</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4829,6 +4829,111 @@
         <v>303</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>2894.83</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0.57425271</v>
+      </c>
+      <c r="E201" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>19389.84</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>3.84639792</v>
+      </c>
+      <c r="E202" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>7103.09</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>1.40905292</v>
+      </c>
+      <c r="E203" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>71555.96000000001</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>14.19468627</v>
+      </c>
+      <c r="E204" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>403160.13</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>79.97561018</v>
+      </c>
+      <c r="E205" t="n">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>403160.13</v>
+        <v>244156.58</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>79.97561018</v>
+        <v>81.26069669</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,82 +509,82 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>71555.96000000001</v>
+        <v>35429.67</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.19468627</v>
+        <v>11.79177587</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19389.84</v>
+        <v>13873.76</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.84639792</v>
+        <v>4.61749343</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7103.09</v>
+        <v>5637.21</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.40905292</v>
+        <v>1.87618786</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2894.83</v>
+        <v>1363.63</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.57425271</v>
+        <v>0.45384615</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>504103.85</v>
+        <v>300460.85</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4934,6 +4934,111 @@
         <v>234</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>13873.76</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>4.61749343</v>
+      </c>
+      <c r="E206" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>5637.21</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>1.87618786</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>1363.63</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>0.45384615</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>35429.67</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>11.79177587</v>
+      </c>
+      <c r="E209" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n">
+        <v>244156.58</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>81.26069669</v>
+      </c>
+      <c r="E210" t="n">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>244156.58</v>
+        <v>251573.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>81.26069669</v>
+        <v>68.32514322</v>
       </c>
       <c r="E2" t="n">
-        <v>297</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,82 +509,82 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>35429.67</v>
+        <v>54619.67</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>11.79177587</v>
+        <v>14.83424116</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13873.76</v>
+        <v>53332.81</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.61749343</v>
+        <v>14.48474085</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5637.21</v>
+        <v>5480.02</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.87618786</v>
+        <v>1.48832716</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1363.63</v>
+        <v>3194.31</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.45384615</v>
+        <v>0.86754762</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>300460.85</v>
+        <v>368199.96</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>340</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5039,6 +5039,111 @@
         <v>297</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n">
+        <v>3194.31</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0.86754762</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>53332.81</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>14.48474085</v>
+      </c>
+      <c r="E212" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>5480.02</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>1.48832716</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n">
+        <v>54619.67</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>14.83424116</v>
+      </c>
+      <c r="E214" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>251573.15</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>68.32514322</v>
+      </c>
+      <c r="E215" t="n">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>251573.15</v>
+        <v>268940.79</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>68.32514322</v>
+        <v>92.1037389</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>54619.67</v>
+        <v>14209.15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.83424116</v>
+        <v>4.86618576</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,61 +530,61 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>53332.81</v>
+        <v>7918.09</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.48474085</v>
+        <v>2.71169611</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5480.02</v>
+        <v>892</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.48832716</v>
+        <v>0.30548187</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3194.31</v>
+        <v>37.66</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.86754762</v>
+        <v>0.01289736</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>368199.96</v>
+        <v>291997.69</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>271</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5144,6 +5144,111 @@
         <v>224</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0.30548187</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>7918.09</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>2.71169611</v>
+      </c>
+      <c r="E217" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0.01289736</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>14209.15</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>4.86618576</v>
+      </c>
+      <c r="E219" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>268940.79</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>92.1037389</v>
+      </c>
+      <c r="E220" t="n">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>268940.79</v>
+        <v>306603.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>92.1037389</v>
+        <v>84.60626838</v>
       </c>
       <c r="E2" t="n">
-        <v>291</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14209.15</v>
+        <v>34911.64</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4.86618576</v>
+        <v>9.6337679</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,52 +530,52 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7918.09</v>
+        <v>17982.75</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.71169611</v>
+        <v>4.96228879</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>892</v>
+        <v>2603.68</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.30548187</v>
+        <v>0.7184781</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37.66</v>
+        <v>287</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01289736</v>
+        <v>0.07919683</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>291997.69</v>
+        <v>362388.22</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5249,6 +5249,111 @@
         <v>291</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0.07919683</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>17982.75</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>4.96228879</v>
+      </c>
+      <c r="E222" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>2603.68</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0.7184781</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>34911.64</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>9.6337679</v>
+      </c>
+      <c r="E224" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>306603.15</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>84.60626838</v>
+      </c>
+      <c r="E225" t="n">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>306603.15</v>
+        <v>255143.11</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>84.60626838</v>
+        <v>81.25473501</v>
       </c>
       <c r="E2" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>34911.64</v>
+        <v>54065.52</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.6337679</v>
+        <v>17.21809968</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>17982.75</v>
+        <v>1908.13</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.96228879</v>
+        <v>0.60767699</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2603.68</v>
+        <v>1788.1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.7184781</v>
+        <v>0.56945136</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>287</v>
+        <v>1099.13</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.07919683</v>
+        <v>0.35003695</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>362388.22</v>
+        <v>314003.99</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>284</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5354,6 +5354,111 @@
         <v>230</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>1099.13</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>0.35003695</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>1908.13</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>0.60767699</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>1788.1</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>0.56945136</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>54065.52</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>17.21809968</v>
+      </c>
+      <c r="E229" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>255143.11</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>81.25473501</v>
+      </c>
+      <c r="E230" t="n">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>255143.11</v>
+        <v>180872.43</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>81.25473501</v>
+        <v>66.28010813</v>
       </c>
       <c r="E2" t="n">
-        <v>215</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>54065.52</v>
+        <v>89030.31</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.21809968</v>
+        <v>32.62486479</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,34 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1908.13</v>
+        <v>2988.23</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.60767699</v>
+        <v>1.09502707</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1788.1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.56945136</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1099.13</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.35003695</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>314003.99</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>272890.97</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>254</v>
+      <c r="E5" s="4" t="n">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5459,6 +5417,69 @@
         <v>215</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>2988.23</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>1.09502707</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>89030.31</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>32.62486479</v>
+      </c>
+      <c r="E232" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>180872.43</v>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>66.28010813</v>
+      </c>
+      <c r="E233" t="n">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>180872.43</v>
+        <v>125310.59</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.28010813</v>
+        <v>57.10461246</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>89030.31</v>
+        <v>66453.41</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>32.62486479</v>
+        <v>30.28312471</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,34 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2988.23</v>
+        <v>27443.48</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.09502707</v>
+        <v>12.50612011</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>232.92</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.10614272</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>272890.97</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>219440.4</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>201</v>
+      <c r="E6" s="4" t="n">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5480,6 +5501,90 @@
         <v>173</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>232.92</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>0.10614272</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>27443.48</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>12.50612011</v>
+      </c>
+      <c r="E235" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>66453.41</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>30.28312471</v>
+      </c>
+      <c r="E236" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>125310.59</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>57.10461246</v>
+      </c>
+      <c r="E237" t="n">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>125310.59</v>
+        <v>334487.78</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>57.10461246</v>
+        <v>76.97542673</v>
       </c>
       <c r="E2" t="n">
-        <v>193</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>66453.41</v>
+        <v>73404.17</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30.28312471</v>
+        <v>16.89244764</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27443.48</v>
+        <v>14439.81</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.50612011</v>
+        <v>3.32302285</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>232.92</v>
+        <v>12206.63</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.10614272</v>
+        <v>2.80910278</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>219440.4</v>
+        <v>434538.39</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>293</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5585,6 +5585,90 @@
         <v>193</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>12206.63</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>2.80910278</v>
+      </c>
+      <c r="E238" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>14439.81</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>3.32302285</v>
+      </c>
+      <c r="E239" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>73404.17</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>16.89244764</v>
+      </c>
+      <c r="E240" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>334487.78</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>76.97542673</v>
+      </c>
+      <c r="E241" t="n">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>334487.78</v>
+        <v>206169.77</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.97542673</v>
+        <v>94.69078374999999</v>
       </c>
       <c r="E2" t="n">
-        <v>270</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>73404.17</v>
+        <v>6938.86</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.89244764</v>
+        <v>3.18691771</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14439.81</v>
+        <v>4414.12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.32302285</v>
+        <v>2.02734127</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12206.63</v>
+        <v>206.75</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.80910278</v>
+        <v>0.09495727</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>434538.39</v>
+        <v>217729.5</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>325</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5669,6 +5669,90 @@
         <v>270</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>4414.12</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>2.02734127</v>
+      </c>
+      <c r="E242" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>206.75</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0.09495727</v>
+      </c>
+      <c r="E243" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>6938.86</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>3.18691771</v>
+      </c>
+      <c r="E244" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>206169.77</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>94.69078374999999</v>
+      </c>
+      <c r="E245" t="n">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,118 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>206169.77</v>
+        <v>369070.94</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>94.69078374999999</v>
+        <v>85.07089664999999</v>
       </c>
       <c r="E2" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6938.86</v>
+        <v>45195.76</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3.18691771</v>
+        <v>10.41762819</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4414.12</v>
+        <v>9882.6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.02734127</v>
+        <v>2.2779405</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>206.75</v>
+        <v>9384.76</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.09495727</v>
+        <v>2.16318832</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>305.19</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.07034633</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>217729.5</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>433839.25</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>246</v>
+      <c r="E7" s="4" t="n">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5753,6 +5774,111 @@
         <v>219</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>45195.76</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>10.41762819</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>9882.6</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>2.2779405</v>
+      </c>
+      <c r="E247" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>305.19</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0.07034633</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>9384.76</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>2.16318832</v>
+      </c>
+      <c r="E249" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>369070.94</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>85.07089664999999</v>
+      </c>
+      <c r="E250" t="n">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,40 +488,40 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>369070.94</v>
+        <v>234809.82</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>85.07089664999999</v>
+        <v>66.50391637</v>
       </c>
       <c r="E2" t="n">
-        <v>218</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45195.76</v>
+        <v>114879.27</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10.41762819</v>
+        <v>32.53663482</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9882.6</v>
+        <v>3000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.2779405</v>
+        <v>0.84967379</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9384.76</v>
+        <v>387.59</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.16318832</v>
+        <v>0.10977502</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>305.19</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.07034633</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>433839.25</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>353076.68</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>263</v>
+      <c r="E6" s="4" t="n">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5879,6 +5858,90 @@
         <v>218</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>0.10977502</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>0.84967379</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>114879.27</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>32.53663482</v>
+      </c>
+      <c r="E253" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>234809.82</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>66.50391637</v>
+      </c>
+      <c r="E254" t="n">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>234809.82</v>
+        <v>103897.6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.50391637</v>
+        <v>62.63198081</v>
       </c>
       <c r="E2" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,76 +509,97 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>114879.27</v>
+        <v>51121.7</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>32.53663482</v>
+        <v>30.81739456</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3000</v>
+        <v>8859.66</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.84967379</v>
+        <v>5.34081687</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>387.59</v>
+        <v>1006.9</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.10977502</v>
+        <v>0.6069836199999999</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.60282413</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>353076.68</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>165885.86</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>241</v>
+      <c r="E7" s="4" t="n">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5942,6 +5963,111 @@
         <v>183</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>8859.66</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>5.34081687</v>
+      </c>
+      <c r="E255" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>1006.9</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>0.6069836199999999</v>
+      </c>
+      <c r="E256" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>0.60282413</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>51121.7</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>30.81739456</v>
+      </c>
+      <c r="E258" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>103897.6</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>62.63198081</v>
+      </c>
+      <c r="E259" t="n">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>103897.6</v>
+        <v>97834.25999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.63198081</v>
+        <v>80.00909722999999</v>
       </c>
       <c r="E2" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>51121.7</v>
+        <v>14869.63</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30.81739456</v>
+        <v>12.1604198</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8859.66</v>
+        <v>7692.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.34081687</v>
+        <v>6.29078176</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1006.9</v>
+        <v>1882.73</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.6069836199999999</v>
+        <v>1.5397012</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.60282413</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>165885.86</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>122278.92</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>211</v>
+      <c r="E6" s="4" t="n">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6068,6 +6047,90 @@
         <v>162</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>7692.3</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>6.29078176</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>1882.73</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1.5397012</v>
+      </c>
+      <c r="E261" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>14869.63</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>12.1604198</v>
+      </c>
+      <c r="E262" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>97834.25999999999</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>80.00909722999999</v>
+      </c>
+      <c r="E263" t="n">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>97834.25999999999</v>
+        <v>185100.03</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.00909722999999</v>
+        <v>71.21069433</v>
       </c>
       <c r="E2" t="n">
-        <v>142</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,76 +509,97 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14869.63</v>
+        <v>50871.54</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.1604198</v>
+        <v>19.571027</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7692.3</v>
+        <v>18435.53</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.29078176</v>
+        <v>7.09241858</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3303.59</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1.27093949</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1882.73</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1.5397012</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>2222.22</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.8549206</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>122278.92</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>259932.91</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>162</v>
+      <c r="E7" s="4" t="n">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6131,6 +6152,111 @@
         <v>142</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>3303.59</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1.27093949</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>18435.53</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>7.09241858</v>
+      </c>
+      <c r="E265" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>2222.22</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>0.8549206</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="n">
+        <v>50871.54</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>19.571027</v>
+      </c>
+      <c r="E267" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>185100.03</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>71.21069433</v>
+      </c>
+      <c r="E268" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
